--- a/medical_surveys_questionnaires/049_water_soluble_vitamins_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/049_water_soluble_vitamins_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -804,8 +804,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,12 +833,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vitamin_supplements'}</t>
+          <t>vitamin_supplements</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vitamin supplements'}</t>
+          <t>Vitamin supplements</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_50_mg'}</t>
+          <t>less_than_50_mg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 50 mg'}</t>
+          <t>Less than 50 mg</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'50-100_mg'}</t>
+          <t>50-100_mg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '50-100 mg'}</t>
+          <t>50-100 mg</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'100-200_mg'}</t>
+          <t>100-200_mg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '100-200 mg'}</t>
+          <t>100-200 mg</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_200_mg'}</t>
+          <t>more_than_200_mg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'More than 200 mg'}</t>
+          <t>More than 200 mg</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'dizziness'}</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Dizziness'}</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'muscle_weakness'}</t>
+          <t>muscle_weakness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Muscle weakness'}</t>
+          <t>Muscle weakness</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
